--- a/ae_ruleresults.xlsx
+++ b/ae_ruleresults.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T21:55:02Z</t>
+          <t>2026-06-09T20:29:42Z</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -743,22 +743,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:57:17Z</t>
+          <t>2026-06-09T23:38:42Z</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Partly Cloudy</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -791,7 +791,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:21:58Z</t>
+          <t>2026-06-09T22:48:04Z</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,10 +803,10 @@
         <v>23</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T20:45:58Z</t>
+          <t>2026-06-09T19:29:48Z</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T21:43:06Z</t>
+          <t>2026-06-09T20:17:43Z</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T22:21:45Z</t>
+          <t>2026-06-09T20:48:45Z</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1062,51 +1062,51 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>S54613</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Warbler</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08T22:14:01Z</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09T20:43:50Z</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Partly Cloudy</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="G13" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:58:51Z</t>
+          <t>2026-06-09T23:40:15Z</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1331,10 +1331,10 @@
         <v>24</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1</v>
@@ -1463,22 +1463,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T23:14:06Z</t>
+          <t>2026-06-09T21:21:59Z</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Partly Cloudy</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>1</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T19:56:57Z</t>
+          <t>2026-06-09T18:09:41Z</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1907,10 +1907,10 @@
         <v>24</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>1</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>97.66374454804765</v>
+        <v>96.50233209789944</v>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
     </row>
@@ -2837,11 +2837,11 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkor MKII Production Meter: Phase current ratio 			 98.16743905668737	 %, PF: 			 0.9967669907722094	</t>
+          <t xml:space="preserve">Elkor MKII Production Meter: Phase current ratio 			 98.7899415135375	 %, PF: 			 0.9970237311753682	</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>98.16743905668737</v>
+        <v>98.7899415135375</v>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="n">
-        <v>76.11583372395667</v>
+        <v>72.1128636475715</v>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>87.08311660951708</v>
+        <v>81.32877012930631</v>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
     </row>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>98.84537369324387</v>
+        <v>98.75341690649442</v>
       </c>
       <c r="H108" s="3" t="inlineStr"/>
     </row>
@@ -5999,11 +5999,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkor Production Meter: Phase current ratio 			 98.78524589008428	 %, PF: 			 0.9939369230430933	</t>
+          <t xml:space="preserve">Elkor Production Meter: Phase current ratio 			 98.86377011036367	 %, PF: 			 0.9946466093466418	</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>98.78524589008428</v>
+        <v>98.86377011036367</v>
       </c>
       <c r="H109" s="3" t="inlineStr"/>
     </row>
@@ -6036,12 +6036,25 @@
       <c r="F110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fail: 0.00 %
-Chint SCA60KTL Inverter - 1: High energy ratio: 			 1.161069073364561	
-Chint SCA60KTL Inverter - 2: High energy ratio: 			 1.2153759682211795	
-Chint SCA60KTL Inverter - 3: High energy ratio: 			 1.1583050881483714	
-Chint SCA60KTL Inverter - 4: High energy ratio: 			 1.1606803553619474	
-Chint SCA60KTL Inverter - 6: High energy ratio: 			 1.1583212489491592	
-Chint SCA60KTL Inverter - 8: High energy ratio: 			 1.158184590816296	</t>
+Chint SCA60KTL Inverter - 1: High energy ratio: 			 1.2089969354714651	
+Chint SCA60KTL Inverter - 2: High energy ratio: 			 1.2582725443346445	
+Chint SCA60KTL Inverter - 3: High energy ratio: 			 1.1770325956389351	
+Chint SCA60KTL Inverter - 4: High energy ratio: 			 1.1988459416632669	
+Chint SCA60KTL Inverter - 6: High energy ratio: 			 1.1881197883876367	
+Chint SCA60KTL Inverter - 7: High energy ratio: 			 1.1041415506648946	
+Chint SCA60KTL Inverter - 8: High energy ratio: 			 1.1606849206995054	
+Chint SCA60KTL Inverter - 9: High energy ratio: 			 1.1219759800675622	
+Chint SCA60KTL Inverter - 10: High energy ratio: 			 1.1219914140705627	
+Chint SCA60KTL Inverter - 11: High energy ratio: 			 1.1194260346583176	
+Chint SCA60KTL Inverter - 12: High energy ratio: 			 1.1231060695104305	
+Chint SCA60KTL Inverter - 17: High energy ratio: 			 1.1066763076123922	
+Chint SCA60KTL Inverter - 19: High energy ratio: 			 1.1168914530978116	
+Chint SCA60KTL Inverter - 21: High energy ratio: 			 1.1219914140705627	
+Chint SCA60KTL Inverter - 22: High energy ratio: 			 1.1015764167939033	
+Chint SCA60KTL Inverter - 23: High energy ratio: 			 1.1117761984305843	
+Chint SCA60KTL Inverter - 24: High energy ratio: 			 1.1117761984305843	
+Chint SCA60KTL Inverter - 25: High energy ratio: 			 1.1015764167936064	
+Chint SCA60KTL Inverter - 26: High energy ratio: 			 1.1117761984305843	</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -6049,7 +6062,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.161069073364561\t', 'success': 0.0, 'hardwareKey': 'H143483', 'hardwareName': 'Chint SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2153759682211795\t', 'success': 0.0, 'hardwareKey': 'H143484', 'hardwareName': 'Chint SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.1583050881483714\t', 'success': 0.0, 'hardwareKey': 'H143485', 'hardwareName': 'Chint SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2089969354714651\t', 'success': 0.0, 'hardwareKey': 'H143483', 'hardwareName': 'Chint SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2582725443346445\t', 'success': 0.0, 'hardwareKey': 'H143484', 'hardwareName': 'Chint SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.1770325956389351\t', 'success': 0.0, 'hardwareKey': 'H143485', 'hardwareName': 'Chint SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -6086,36 +6099,44 @@
       <c r="H111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>S44566</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>RIT</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>PVlosses</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H112" s="3" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Chint SCA60KTL Inverter - 2: Excessive residual loss: 			 -27.638771185798994	 %</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -27.638771185798994\t %', 'success': 0.0, 'hardwareKey': 'H143484', 'hardwareName': 'Chint SCA60KTL Inverter - 2', 'isAcknowledged': False}</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -6145,7 +6166,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" s="3" t="n">
-        <v>106.9526920938529</v>
+        <v>109.9134133982952</v>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
     </row>
@@ -6774,7 +6795,7 @@
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>99.42380248961044</v>
+        <v>99.44293194820601</v>
       </c>
       <c r="H131" s="3" t="inlineStr"/>
     </row>
@@ -6806,11 +6827,11 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkor Production Meter: Phase current ratio 			 97.4646032268686	 %, PF: 			 0.9994117397888141	</t>
+          <t xml:space="preserve">Elkor Production Meter: Phase current ratio 			 99.51386009064436	 %, PF: 			 0.9990911657189555	</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>97.4646032268686</v>
+        <v>99.51386009064436</v>
       </c>
       <c r="H132" s="3" t="inlineStr"/>
     </row>
@@ -6843,33 +6864,33 @@
       <c r="F133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fail: 0.00 %
-Solectria PVI 60KTL Inverter - 1: High energy ratio: 			 1.2408658892274098	
-Solectria PVI 60KTL Inverter - 2: High energy ratio: 			 1.292035616618231	
-Solectria PVI 60KTL Inverter - 3: High energy ratio: 			 1.2613337801837383	
-Solectria PVI 60KTL Inverter - 4: High energy ratio: 			 1.2715677256619025	
-Solectria PVI 60KTL Inverter - 5: High energy ratio: 			 1.2587752938140482	
-Solectria PVI 60KTL Inverter - 6: High energy ratio: 			 1.2664507529228204	
-Solectria PVI 60KTL Inverter - 7: High energy ratio: 			 1.2818016711400666	
-Solectria PVI 60KTL Inverter - 8: High energy ratio: 			 1.2945941029877719	
-Solectria PVI 60KTL Inverter - 9: High energy ratio: 			 1.18969616183644	
-Solectria PVI 60KTL Inverter - 10: High energy ratio: 			 1.2843601575097567	
-Solectria PVI 60KTL Inverter - 11: High energy ratio: 			 1.2843601575096077	
-Solectria PVI 60KTL Inverter - 12: High energy ratio: 			 1.304828048466085	
-Solectria PVI 60KTL Inverter - 13: High energy ratio: 			 1.2861258734548071	
-Solectria PVI 60KTL Inverter - 14: High energy ratio: 			 1.3073865348354772	
-Solectria PVI 60KTL Inverter - 15: High energy ratio: 			 1.2664507529229694	
-Solectria PVI 60KTL Inverter - 16: High energy ratio: 			 1.2741262120315924	
-Solectria PVI 60KTL Inverter - 17: High energy ratio: 			 1.2843601575096077	
-Solectria PVI 60KTL Inverter - 18: High energy ratio: 			 1.199930107314753	
-Solectria PVI 60KTL Inverter - 19: High energy ratio: 			 1.3091243746336392	
-Solectria PVI 60KTL Inverter - 21: High energy ratio: 			 1.302269562096395	
-Solectria PVI 60KTL Inverter - 22: High energy ratio: 			 1.207605566423525	
-Solectria PVI 60KTL Inverter - 23: High energy ratio: 			 1.297152589357313	
-Solectria PVI 60KTL Inverter - 24: High energy ratio: 			 1.253658321075115	
-Solectria PVI 60KTL Inverter - 25: High energy ratio: 			 1.2843601575096077	
-Solectria PVI 60KTL Inverter - 26: High energy ratio: 			 1.2988502765744891	
-Solectria PVI 60KTL Inverter - 27: High energy ratio: 			 1.2945941029877719	
-Elkor Production Meter: High energy ratio: 			 1.2193556519723794	</t>
+Solectria PVI 60KTL Inverter - 1: High energy ratio: 			 1.2041837618641495	
+Solectria PVI 60KTL Inverter - 2: High energy ratio: 			 1.2623407210814945	
+Solectria PVI 60KTL Inverter - 3: High energy ratio: 			 1.2267322269432464	
+Solectria PVI 60KTL Inverter - 4: High energy ratio: 			 1.2385525949431688	
+Solectria PVI 60KTL Inverter - 5: High energy ratio: 			 1.211846800503255	
+Solectria PVI 60KTL Inverter - 6: High energy ratio: 			 1.2356302983393237	
+Solectria PVI 60KTL Inverter - 7: High energy ratio: 			 1.2438263515766639	
+Solectria PVI 60KTL Inverter - 8: High energy ratio: 			 1.264693635817369	
+Solectria PVI 60KTL Inverter - 9: High energy ratio: 			 1.1536698970370964	
+Solectria PVI 60KTL Inverter - 10: High energy ratio: 			 1.2514579461563946	
+Solectria PVI 60KTL Inverter - 11: High energy ratio: 			 1.2438135873411529	
+Solectria PVI 60KTL Inverter - 12: High energy ratio: 			 1.2725971037954678	
+Solectria PVI 60KTL Inverter - 13: High energy ratio: 			 1.2470453874077723	
+Solectria PVI 60KTL Inverter - 14: High energy ratio: 			 1.2679680967619689	
+Solectria PVI 60KTL Inverter - 15: High energy ratio: 			 1.223243575288155	
+Solectria PVI 60KTL Inverter - 16: High energy ratio: 			 1.2338069585537705	
+Solectria PVI 60KTL Inverter - 17: High energy ratio: 			 1.244370432085417	
+Solectria PVI 60KTL Inverter - 18: High energy ratio: 			 1.1595751337358406	
+Solectria PVI 60KTL Inverter - 19: High energy ratio: 			 1.27080019496231	
+Solectria PVI 60KTL Inverter - 21: High energy ratio: 			 1.2707848584790944	
+Solectria PVI 60KTL Inverter - 22: High energy ratio: 			 1.1630345911474984	
+Solectria PVI 60KTL Inverter - 23: High energy ratio: 			 1.2679429847341064	
+Solectria PVI 60KTL Inverter - 24: High energy ratio: 			 1.20996797595023	
+Solectria PVI 60KTL Inverter - 25: High energy ratio: 			 1.250089261903829	
+Solectria PVI 60KTL Inverter - 26: High energy ratio: 			 1.2549034033357818	
+Solectria PVI 60KTL Inverter - 27: High energy ratio: 			 1.2581919667868393	
+Elkor Production Meter: High energy ratio: 			 1.1840645474834195	</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
@@ -6877,7 +6898,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2408658892274098\t', 'success': 0.0, 'hardwareKey': 'H155939', 'hardwareName': 'Solectria PVI 60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.292035616618231\t', 'success': 0.0, 'hardwareKey': 'H155940', 'hardwareName': 'Solectria PVI 60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2613337801837383\t', 'success': 0.0, 'hardwareKey': 'H155941', 'hardwareName': 'Solectria PVI 60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2041837618641495\t', 'success': 0.0, 'hardwareKey': 'H155939', 'hardwareName': 'Solectria PVI 60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2623407210814945\t', 'success': 0.0, 'hardwareKey': 'H155940', 'hardwareName': 'Solectria PVI 60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.2267322269432464\t', 'success': 0.0, 'hardwareKey': 'H155941', 'hardwareName': 'Solectria PVI 60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -6942,29 +6963,23 @@
       <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Fail: 0.00 %
-Solectria PVI 60KTL Inverter - 2: Excessive residual loss: 			 -29.983261425510428	 %
-Solectria PVI 60KTL Inverter - 3: Excessive residual loss: 			 -26.678816982178216	 %
-Solectria PVI 60KTL Inverter - 4: Excessive residual loss: 			 -27.543032704779787	 %
-Solectria PVI 60KTL Inverter - 5: Excessive residual loss: 			 -26.308882581474236	 %
-Solectria PVI 60KTL Inverter - 6: Excessive residual loss: 			 -27.277119646811286	 %
-Solectria PVI 60KTL Inverter - 7: Excessive residual loss: 			 -29.060270604408572	 %
-Solectria PVI 60KTL Inverter - 8: Excessive residual loss: 			 -29.88038793550123	 %
-Solectria PVI 60KTL Inverter - 10: Excessive residual loss: 			 -28.53790340942045	 %
-Solectria PVI 60KTL Inverter - 11: Excessive residual loss: 			 -29.01987149876664	 %
-Solectria PVI 60KTL Inverter - 12: Excessive residual loss: 			 -31.19148230304562	 %
-Solectria PVI 60KTL Inverter - 13: Excessive residual loss: 			 -29.169191838597357	 %
-Solectria PVI 60KTL Inverter - 14: Excessive residual loss: 			 -31.704960668911607	 %
-Solectria PVI 60KTL Inverter - 15: Excessive residual loss: 			 -27.38547311799452	 %
-Solectria PVI 60KTL Inverter - 16: Excessive residual loss: 			 -28.126549748559544	 %
-Solectria PVI 60KTL Inverter - 17: Excessive residual loss: 			 -29.249537077992983	 %
-Solectria PVI 60KTL Inverter - 19: Excessive residual loss: 			 -31.4467616390621	 %
-Solectria PVI 60KTL Inverter - 20: Downtime loss detected: 			 99.62318600262489	 % (			 389.99333549999994	 kWh)
-Solectria PVI 60KTL Inverter - 21: Excessive residual loss: 			 -30.39706892835074	 %
-Solectria PVI 60KTL Inverter - 23: Excessive residual loss: 			 -29.91894571903364	 %
-Solectria PVI 60KTL Inverter - 24: Excessive residual loss: 			 -26.08397389474188	 %
-Solectria PVI 60KTL Inverter - 25: Excessive residual loss: 			 -28.642274886636304	 %
-Solectria PVI 60KTL Inverter - 26: Excessive residual loss: 			 -30.30688276240013	 %
-Solectria PVI 60KTL Inverter - 27: Excessive residual loss: 			 -29.923768535615352	 %</t>
+Solectria PVI 60KTL Inverter - 2: Excessive residual loss: 			 -26.882887668811083	 %
+Solectria PVI 60KTL Inverter - 7: Excessive residual loss: 			 -25.97612248923593	 %
+Solectria PVI 60KTL Inverter - 8: Excessive residual loss: 			 -29.350297541602682	 %
+Solectria PVI 60KTL Inverter - 10: Excessive residual loss: 			 -25.791662093639818	 %
+Solectria PVI 60KTL Inverter - 11: Excessive residual loss: 			 -26.005916640471455	 %
+Solectria PVI 60KTL Inverter - 12: Excessive residual loss: 			 -28.429706158279433	 %
+Solectria PVI 60KTL Inverter - 13: Excessive residual loss: 			 -26.13947921598428	 %
+Solectria PVI 60KTL Inverter - 14: Excessive residual loss: 			 -28.582033238286762	 %
+Solectria PVI 60KTL Inverter - 16: Excessive residual loss: 			 -25.069641954141535	 %
+Solectria PVI 60KTL Inverter - 17: Excessive residual loss: 			 -25.956719516662087	 %
+Solectria PVI 60KTL Inverter - 19: Excessive residual loss: 			 -28.355013409640605	 %
+Solectria PVI 60KTL Inverter - 20: Downtime loss detected: 			 99.73033626314088	 % (			 385.93883370000003	 kWh)
+Solectria PVI 60KTL Inverter - 21: Excessive residual loss: 			 -27.979631163101004	 %
+Solectria PVI 60KTL Inverter - 23: Excessive residual loss: 			 -27.20085864065394	 %
+Solectria PVI 60KTL Inverter - 25: Excessive residual loss: 			 -25.32229519450897	 %
+Solectria PVI 60KTL Inverter - 26: Excessive residual loss: 			 -26.55147779327786	 %
+Solectria PVI 60KTL Inverter - 27: Excessive residual loss: 			 -26.574988271676748	 %</t>
         </is>
       </c>
       <c r="G135" s="2" t="n">
@@ -6972,49 +6987,41 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -29.983261425510428\t %', 'success': 0.0, 'hardwareKey': 'H155940', 'hardwareName': 'Solectria PVI 60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -26.678816982178216\t %', 'success': 0.0, 'hardwareKey': 'H155941', 'hardwareName': 'Solectria PVI 60KTL Inverter - 3', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -27.543032704779787\t %', 'success': 0.0, 'hardwareKey': 'H155942', 'hardwareName': 'Solectria PVI 60KTL Inverter - 4', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -26.882887668811083\t %', 'success': 0.0, 'hardwareKey': 'H155940', 'hardwareName': 'Solectria PVI 60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -25.97612248923593\t %', 'success': 0.0, 'hardwareKey': 'H155945', 'hardwareName': 'Solectria PVI 60KTL Inverter - 7', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t -29.350297541602682\t %', 'success': 0.0, 'hardwareKey': 'H155946', 'hardwareName': 'Solectria PVI 60KTL Inverter - 8', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>S44882</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>Monroe Landfill</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>PVmodelEnergy24</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Energy above expected (			 121.9355705654503	 %)</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>121.9355705654503</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Energy above expected (\t\t\t 121.9355705654503\t %)', 'success': 1.219355705654503, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
-        </is>
-      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="n">
+        <v>118.4064596119078</v>
+      </c>
+      <c r="H136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -7145,8 +7152,10 @@
       <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Fail: 0.00 %
-CPS SCA60KTL Inverter - 1: Inverter uptime: 			 93.2203389830509	 %
-			 1	 of 			 3	 inverters failed to achieve an uptime of 			 100	 %</t>
+CPS SCA60KTL Inverter - 1: Inverter uptime: 			 91.3793103448276	 %
+CPS SCA60KTL Inverter - 2: Inverter uptime: 			 88.6363636363636	 %
+CPS SCA60KTL Inverter - 3: Inverter uptime: 			 88.6363636363636	 %
+			 3	 of 			 3	 inverters failed to achieve an uptime of 			 100	 %</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -7154,7 +7163,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 93.2203389830509\t %', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': '\t\t\t 1\t of \t\t\t 3\t inverters failed to achieve an uptime of \t\t\t 100\t %', 'success': 0.0, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 91.3793103448276\t %', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 88.6363636363636\t %', 'success': 0.0, 'hardwareKey': 'H226502', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 88.6363636363636\t %', 'success': 0.0, 'hardwareKey': 'H226503', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7621,7 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>99.46480421363623</v>
+        <v>99.6321123532075</v>
       </c>
       <c r="H154" s="3" t="inlineStr"/>
     </row>
@@ -7644,11 +7653,11 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AcuRev Production Meter: Phase current ratio 			 99.04501082043157	 %, PF: 			 0.998958815622717	</t>
+          <t>AcuRev Production Meter: Phase current ratio 			 99.06269563402812	 %, PF: not available</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>99.04501082043157</v>
+        <v>99.06269563402812</v>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
     </row>
@@ -7681,10 +7690,10 @@
       <c r="F156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fail: 0.00 %
-CPS SCA60KTL Inverter - 1: Low energy ratio: 			 0.49134283833021897	
-CPS SCA60KTL Inverter - 2: Low energy ratio: 			 0.4452724910224106	
-CPS SCA60KTL Inverter - 3: Low energy ratio: 			 0.4722442660397089	
-AcuRev Production Meter: Low energy ratio: 			 0.4721553282941796	</t>
+CPS SCA60KTL Inverter - 1: Low energy ratio: 			 0.3039669274311958	
+CPS SCA60KTL Inverter - 2: Low energy ratio: 			 0.33737292529534346	
+CPS SCA60KTL Inverter - 3: Low energy ratio: 			 0.3593369811412304	
+AcuRev Production Meter: Low energy ratio: 			 0.33466001395812806	</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
@@ -7692,7 +7701,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.49134283833021897\t', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.4452724910224106\t', 'success': 0.0, 'hardwareKey': 'H226502', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.4722442660397089\t', 'success': 0.0, 'hardwareKey': 'H226503', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.3039669274311958\t', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.33737292529534346\t', 'success': 0.0, 'hardwareKey': 'H226502', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.3593369811412304\t', 'success': 0.0, 'hardwareKey': 'H226503', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -7757,9 +7766,9 @@
       <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Fail: 0.00 %
-CPS SCA60KTL Inverter - 1: Excessive residual loss: 			 50.1452670004859	 %
-CPS SCA60KTL Inverter - 2: Excessive residual loss: 			 51.57073288594476	 %
-CPS SCA60KTL Inverter - 3: Excessive residual loss: 			 48.59383692383666	 %</t>
+CPS SCA60KTL Inverter - 1: Excessive residual loss: 			 62.24340331484645	 %
+CPS SCA60KTL Inverter - 2: Excessive residual loss: 			 58.05768907220828	 %
+CPS SCA60KTL Inverter - 3: Excessive residual loss: 			 55.192431062835524	 %</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
@@ -7767,7 +7776,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 50.1452670004859\t %', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 51.57073288594476\t %', 'success': 0.0, 'hardwareKey': 'H226502', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 48.59383692383666\t %', 'success': 0.0, 'hardwareKey': 'H226503', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 62.24340331484645\t %', 'success': 0.0, 'hardwareKey': 'H226501', 'hardwareName': 'CPS SCA60KTL Inverter - 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 58.05768907220828\t %', 'success': 0.0, 'hardwareKey': 'H226502', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 55.192431062835524\t %', 'success': 0.0, 'hardwareKey': 'H226503', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -7799,15 +7808,15 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Energy below expected (			 47.21553299205142	 %)</t>
+          <t>Energy below expected (			 33.466001385897506	 %)</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>47.21553299205142</v>
+        <v>33.46600138589751</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Energy below expected (\t\t\t 47.21553299205142\t %)', 'success': 0.47215532992051423, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Energy below expected (\t\t\t 33.466001385897506\t %)', 'success': 0.3346600138589751, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8422,7 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>99.37234274936175</v>
+        <v>99.2169471870174</v>
       </c>
       <c r="H177" s="3" t="inlineStr"/>
     </row>
@@ -8445,11 +8454,11 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AcuRev Production Meter: Phase current ratio 			 98.99580065793423	 %, PF: 			 0.9969694256969085	</t>
+          <t xml:space="preserve">AcuRev Production Meter: Phase current ratio 			 98.89886261952063	 %, PF: 			 0.9968171070189442	</t>
         </is>
       </c>
       <c r="G178" s="3" t="n">
-        <v>98.99580065793423</v>
+        <v>98.89886261952063</v>
       </c>
       <c r="H178" s="3" t="inlineStr"/>
     </row>
@@ -8481,7 +8490,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr"/>
       <c r="G179" s="3" t="n">
-        <v>82.41146477152915</v>
+        <v>81.96526412120663</v>
       </c>
       <c r="H179" s="3" t="inlineStr"/>
     </row>
@@ -8577,7 +8586,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>90.24824969690737</v>
+        <v>96.40053726132119</v>
       </c>
       <c r="H182" s="3" t="inlineStr"/>
     </row>
@@ -9975,7 +9984,7 @@
         </is>
       </c>
       <c r="G223" s="3" t="n">
-        <v>99.71641494395197</v>
+        <v>99.06755127247069</v>
       </c>
       <c r="H223" s="3" t="inlineStr"/>
     </row>
@@ -10007,11 +10016,11 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AcuRev Production Meter: Phase current ratio 			 99.69143907952218	 %, PF: 			 0.9994430438565858	</t>
+          <t xml:space="preserve">AcuRev Production Meter: Phase current ratio 			 99.67600915955414	 %, PF: 			 0.9994070594968806	</t>
         </is>
       </c>
       <c r="G224" s="3" t="n">
-        <v>99.69143907952218</v>
+        <v>99.67600915955414</v>
       </c>
       <c r="H224" s="3" t="inlineStr"/>
     </row>
@@ -10044,8 +10053,8 @@
       <c r="F225" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fail: 0.00 %
-CPS SCA60KTL Inverter - 2: Low energy ratio: 			 0.6910718772360964	
-CPS SCA60KTL Inverter - 3: Low energy ratio: 			 0.6461587270465415	</t>
+CPS SCA60KTL Inverter - 2: Low energy ratio: 			 0.6666237385604515	
+CPS SCA60KTL Inverter - 3: Low energy ratio: 			 0.6177337693054668	</t>
         </is>
       </c>
       <c r="G225" s="2" t="n">
@@ -10053,7 +10062,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.6910718772360964\t', 'success': 0.0, 'hardwareKey': 'H226527', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.6461587270465415\t', 'success': 0.0, 'hardwareKey': 'H226528', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.6666237385604515\t', 'success': 0.0, 'hardwareKey': 'H226527', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Low energy ratio: \t\t\t 0.6177337693054668\t', 'success': 0.0, 'hardwareKey': 'H226528', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -10118,8 +10127,8 @@
       <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Fail: 0.00 %
-CPS SCA60KTL Inverter - 2: Excessive residual loss: 			 28.66594597069033	 %
-CPS SCA60KTL Inverter - 3: Excessive residual loss: 			 33.061322534542796	 %</t>
+CPS SCA60KTL Inverter - 2: Excessive residual loss: 			 29.381059597673698	 %
+CPS SCA60KTL Inverter - 3: Excessive residual loss: 			 34.39888189568981	 %</t>
         </is>
       </c>
       <c r="G227" s="2" t="n">
@@ -10127,7 +10136,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 28.66594597069033\t %', 'success': 0.0, 'hardwareKey': 'H226527', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 33.061322534542796\t %', 'success': 0.0, 'hardwareKey': 'H226528', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 29.381059597673698\t %', 'success': 0.0, 'hardwareKey': 'H226527', 'hardwareName': 'CPS SCA60KTL Inverter - 2', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Excessive residual loss: \t\t\t 34.39888189568981\t %', 'success': 0.0, 'hardwareKey': 'H226528', 'hardwareName': 'CPS SCA60KTL Inverter - 3', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -10159,15 +10168,15 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Energy below expected (			 78.40526038391509	 %)</t>
+          <t>Energy below expected (			 73.88444803804886	 %)</t>
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>78.40526038391509</v>
+        <v>73.88444803804886</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Energy below expected (\t\t\t 78.40526038391509\t %)', 'success': 0.784052603839151, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Energy below expected (\t\t\t 73.88444803804886\t %)', 'success': 0.7388444803804886, 'hardwareKey': '', 'hardwareName': '', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -11018,75 +11027,36 @@
       <c r="H253" s="3" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+      <c r="A254" s="3" t="inlineStr">
         <is>
           <t>S54613</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B254" s="3" t="inlineStr">
         <is>
           <t>Warbler</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" s="3" t="inlineStr">
         <is>
           <t>Availability</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>Fail: 0.00 %
-Sungrow SG125 Inverter A1 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A2 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A3 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A4 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter A5 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter A6 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A7 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A8 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A9 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A10 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A11 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A12 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A13 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter A14 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter A15 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter A16 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B17 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B18 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B20 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B21 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B22 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B23 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B24 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B25 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B26 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B27 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter B28 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B29 at 100%: Availability: 			 95.74468085106383	 %
-Sungrow SG125 Inverter B30 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B31 at 100%: Availability: 			 97.87234042553192	 %
-Sungrow SG125 Inverter B32 at 100%: Availability: 			 97.87234042553192	 %</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Availability: \t\t\t 97.87234042553192\t %', 'success': 0.0, 'hardwareKey': 'H263557', 'hardwareName': 'Sungrow SG125 Inverter A1 at 100%', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Availability: \t\t\t 97.87234042553192\t %', 'success': 0.0, 'hardwareKey': 'H263558', 'hardwareName': 'Sungrow SG125 Inverter A2 at 100%', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Availability: \t\t\t 97.87234042553192\t %', 'success': 0.0, 'hardwareKey': 'H263559', 'hardwareName': 'Sungrow SG125 Inverter A3 at 100%', 'isAcknowledged': False}</t>
-        </is>
-      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr"/>
+      <c r="G254" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -11121,76 +11091,36 @@
       <c r="H255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+      <c r="A256" s="3" t="inlineStr">
         <is>
           <t>S54613</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B256" s="3" t="inlineStr">
         <is>
           <t>Warbler</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C256" s="3" t="inlineStr">
         <is>
           <t>InverterUptime</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>Fail: 0.00 %
-Sungrow SG125 Inverter A1 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A2 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A3 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A4 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter A5 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter A6 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A7 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A8 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A9 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A10 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A11 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A12 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A13 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter A14 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter A15 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter A16 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B17 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B18 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B20 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B21 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B22 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B23 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B24 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B25 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B26 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B27 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter B28 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B29 at 100%: Inverter uptime: 			 95.7446808510638	 %
-Sungrow SG125 Inverter B30 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B31 at 100%: Inverter uptime: 			 97.8723404255319	 %
-Sungrow SG125 Inverter B32 at 100%: Inverter uptime: 			 97.8723404255319	 %
-			 31	 of 			 32	 inverters failed to achieve an uptime of 			 100	 %</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 97.8723404255319\t %', 'success': 0.0, 'hardwareKey': 'H263557', 'hardwareName': 'Sungrow SG125 Inverter A1 at 100%', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 97.8723404255319\t %', 'success': 0.0, 'hardwareKey': 'H263558', 'hardwareName': 'Sungrow SG125 Inverter A2 at 100%', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Inverter uptime: \t\t\t 97.8723404255319\t %', 'success': 0.0, 'hardwareKey': 'H263559', 'hardwareName': 'Sungrow SG125 Inverter A3 at 100%', 'isAcknowledged': False}</t>
-        </is>
-      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr"/>
+      <c r="G256" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -11648,7 +11578,7 @@
         </is>
       </c>
       <c r="G270" s="3" t="n">
-        <v>98.80459770114942</v>
+        <v>98.60909090909091</v>
       </c>
       <c r="H270" s="3" t="inlineStr"/>
     </row>
@@ -11680,11 +11610,11 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEL 735 Production Meter: Phase current ratio 			 99.79381443298969	 %, PF: 			 1	</t>
+          <t xml:space="preserve">SEL 735 Production Meter: Phase current ratio 			 99.24528301886792	 %, PF: 			 1	</t>
         </is>
       </c>
       <c r="G271" s="3" t="n">
-        <v>99.79381443298969</v>
+        <v>99.24528301886792</v>
       </c>
       <c r="H271" s="3" t="inlineStr"/>
     </row>
@@ -11716,7 +11646,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr"/>
       <c r="G272" s="3" t="n">
-        <v>89.88634</v>
+        <v>72.70453907072623</v>
       </c>
       <c r="H272" s="3" t="inlineStr"/>
     </row>
@@ -11812,7 +11742,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr"/>
       <c r="G275" s="3" t="n">
-        <v>89.88612331036441</v>
+        <v>81.91625572024147</v>
       </c>
       <c r="H275" s="3" t="inlineStr"/>
     </row>
@@ -11844,11 +11774,11 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Slight losses or device availability issues should be addressed during the next scheduled maintenance activity.</t>
+          <t>All equipment operating normally</t>
         </is>
       </c>
       <c r="G276" s="3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H276" s="3" t="inlineStr"/>
     </row>
@@ -15930,7 +15860,7 @@
         </is>
       </c>
       <c r="G385" s="3" t="n">
-        <v>95.47727272727273</v>
+        <v>98.06018518518519</v>
       </c>
       <c r="H385" s="3" t="inlineStr"/>
     </row>
@@ -16004,53 +15934,45 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ION 8650 Production Meter: Phase current ratio 			 99.8774765643334	 %, PF: 			 0.9984334821381202	</t>
+          <t xml:space="preserve">ION 8650 Production Meter: Phase current ratio 			 99.91867278584503	 %, PF: 			 0.9983377367760133	</t>
         </is>
       </c>
       <c r="G387" s="3" t="n">
-        <v>99.87747656433341</v>
+        <v>99.91867278584503</v>
       </c>
       <c r="H387" s="3" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="inlineStr">
+      <c r="A388" s="3" t="inlineStr">
         <is>
           <t>S63839</t>
         </is>
       </c>
-      <c r="B388" s="2" t="inlineStr">
+      <c r="B388" s="3" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C388" s="2" t="inlineStr">
+      <c r="C388" s="3" t="inlineStr">
         <is>
           <t>EnergyRatio</t>
         </is>
       </c>
-      <c r="D388" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F388" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inverter 24: High energy ratio: 			 1.1002364656703594	</t>
-        </is>
-      </c>
-      <c r="G388" s="2" t="n">
-        <v>89.97635343296406</v>
-      </c>
-      <c r="H388" s="2" t="inlineStr">
-        <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.1002364656703594\t', 'success': 0.8997635343296406, 'hardwareKey': 'H401001', 'hardwareName': 'Inverter 24', 'isAcknowledged': False}</t>
-        </is>
-      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F388" s="3" t="inlineStr"/>
+      <c r="G388" s="3" t="n">
+        <v>95.55145981006639</v>
+      </c>
+      <c r="H388" s="3" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -16144,7 +16066,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr"/>
       <c r="G391" s="3" t="n">
-        <v>102.0255729333683</v>
+        <v>101.0086298528736</v>
       </c>
       <c r="H391" s="3" t="inlineStr"/>
     </row>
@@ -17902,7 +17824,7 @@
       <c r="F441" s="2" t="inlineStr">
         <is>
           <t>Fail: 0.00 %
-TRACKER CONTROL (ST1): Availability: 			 54.736842105263165	 %
+TRACKER CONTROL (ST1): Availability: 			 53.68421052631579	 %
 12 String INV's: Availability: 			 0	 %
 13 String INV's: Availability: 			 0	 %</t>
         </is>
@@ -17912,7 +17834,7 @@
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Availability: \t\t\t 54.736842105263165\t %', 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Availability: \t\t\t 0\t %', 'success': 0.0, 'hardwareKey': 'H595430', 'hardwareName': "12 String INV's", 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Availability: \t\t\t 0\t %', 'success': 0.0, 'hardwareKey': 'H595436', 'hardwareName': "13 String INV's", 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Availability: \t\t\t 53.68421052631579\t %', 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'Availability: \t\t\t 0\t %', 'success': 0.0, 'hardwareKey': 'H595430', 'hardwareName': "12 String INV's", 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Availability: \t\t\t 0\t %', 'success': 0.0, 'hardwareKey': 'H595436', 'hardwareName': "13 String INV's", 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17866,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRACKER CONTROL (ST1): Last upload: 			 6/8/2026 8:56 AM	 (			 US/Eastern	), delay: 			 10.3 h	</t>
+          <t xml:space="preserve">TRACKER CONTROL (ST1): Last upload: 			 6/9/2026 10:16 AM	 (			 US/Eastern	), delay: 			 7.1 h	</t>
         </is>
       </c>
       <c r="G442" s="2" t="n">
@@ -17952,7 +17874,7 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': 'Last upload: \t\t\t 6/8/2026 8:56 AM\t (\t\t\t US/Eastern\t), delay: \t\t\t 10.3 h\t', 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': 'Last upload: \t\t\t 6/9/2026 10:16 AM\t (\t\t\t US/Eastern\t), delay: \t\t\t 7.1 h\t', 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -18336,36 +18258,44 @@
       <c r="H453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="3" t="inlineStr">
+      <c r="A454" s="2" t="inlineStr">
         <is>
           <t>S64603</t>
         </is>
       </c>
-      <c r="B454" s="3" t="inlineStr">
+      <c r="B454" s="2" t="inlineStr">
         <is>
           <t>Shorthorn</t>
         </is>
       </c>
-      <c r="C454" s="3" t="inlineStr">
+      <c r="C454" s="2" t="inlineStr">
         <is>
           <t>CheckWeather</t>
         </is>
       </c>
-      <c r="D454" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E454" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F454" s="3" t="inlineStr"/>
-      <c r="G454" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H454" s="3" t="inlineStr"/>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>PYRANOMETER - POA: The POA sensor, "", appears to be fixed tilt and is configured for a tracker.</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>{'index': 0, 'result': 3, 'detail': 'The POA sensor, "", appears to be fixed tilt and is configured for a tracker.', 'success': 0.0, 'hardwareKey': 'H422139', 'hardwareName': 'PYRANOMETER - POA', 'isAcknowledged': False}</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -18463,7 +18393,7 @@
         </is>
       </c>
       <c r="G457" s="3" t="n">
-        <v>98.2715954895658</v>
+        <v>98.16391223821057</v>
       </c>
       <c r="H457" s="3" t="inlineStr"/>
     </row>
@@ -18497,8 +18427,16 @@
         <is>
           <t>Fail: 0.00 %
 TRACKER CONTROL (ST0): Tracker '			 Position A1 S 44	' always 			 0	 degrees
+TRACKER CONTROL (ST1): Tracker '			 Position A1 S 70	' always 			 0	 degrees
+TRACKER CONTROL (ST1): Tracker '			 Position A1 S 116	' always 			 0	 degrees
 TRACKER CONTROL (ST2): Tracker '			 Position A1 S 77	' always 			 0	 degrees
-TRACKER CONTROL (ST2): Average tracker error (			 Position A1 S 25	): 			 33.88015	 degrees</t>
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 16	): 			 10.19743	 degrees
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 27	): 			 90.48487	 degrees
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 48	): 			 45.15386	 degrees
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 54	): 			 16.76591	 degrees
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 68	): 			 101.5587	 degrees
+TRACKER CONTROL (ST1): Average tracker error (			 Position A1 S 118	): 			 5.277579	 degrees
+TRACKER CONTROL (ST2): Average tracker error (			 Position A1 S 25	): 			 46.618025	 degrees</t>
         </is>
       </c>
       <c r="G458" s="2" t="n">
@@ -18506,7 +18444,7 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>{'index': 0, 'result': 3, 'detail': "Tracker '\t\t\t Position A1 S 44\t' always \t\t\t 0\t degrees", 'success': 0.0, 'hardwareKey': 'H422144', 'hardwareName': 'TRACKER CONTROL (ST0)', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': "Tracker '\t\t\t Position A1 S 77\t' always \t\t\t 0\t degrees", 'success': 0.0, 'hardwareKey': 'H422146', 'hardwareName': 'TRACKER CONTROL (ST2)', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': 'Average tracker error (\t\t\t Position A1 S 25\t): \t\t\t 33.88015\t degrees', 'success': 0.0, 'hardwareKey': 'H422146', 'hardwareName': 'TRACKER CONTROL (ST2)', 'isAcknowledged': False}</t>
+          <t>{'index': 0, 'result': 3, 'detail': "Tracker '\t\t\t Position A1 S 44\t' always \t\t\t 0\t degrees", 'success': 0.0, 'hardwareKey': 'H422144', 'hardwareName': 'TRACKER CONTROL (ST0)', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': "Tracker '\t\t\t Position A1 S 70\t' always \t\t\t 0\t degrees", 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}, {'index': 2, 'result': 3, 'detail': "Tracker '\t\t\t Position A1 S 116\t' always \t\t\t 0\t degrees", 'success': 0.0, 'hardwareKey': 'H422145', 'hardwareName': 'TRACKER CONTROL (ST1)', 'isAcknowledged': False}</t>
         </is>
       </c>
     </row>
@@ -18538,11 +18476,11 @@
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">METER - PRODUCTION: Phase current ratio 			 97.78703487158398	 %, PF: 			 0.980000003315249	</t>
+          <t xml:space="preserve">METER - PRODUCTION: Phase current ratio 			 98.22341930781255	 %, PF: 			 0.980000003315249	</t>
         </is>
       </c>
       <c r="G459" s="3" t="n">
-        <v>97.78703487158398</v>
+        <v>98.22341930781255</v>
       </c>
       <c r="H459" s="3" t="inlineStr"/>
     </row>
@@ -18574,7 +18512,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr"/>
       <c r="G460" s="3" t="n">
-        <v>92.41385536040187</v>
+        <v>92.47296235392383</v>
       </c>
       <c r="H460" s="3" t="inlineStr"/>
     </row>
@@ -18670,7 +18608,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr"/>
       <c r="G463" s="3" t="n">
-        <v>99.41986266029645</v>
+        <v>98.55923162482674</v>
       </c>
       <c r="H463" s="3" t="inlineStr"/>
     </row>
@@ -26481,7 +26419,7 @@
         </is>
       </c>
       <c r="G668" s="3" t="n">
-        <v>98.29954504765516</v>
+        <v>98.00177477882255</v>
       </c>
       <c r="H668" s="3" t="inlineStr"/>
     </row>
@@ -26545,45 +26483,55 @@
       </c>
       <c r="F670" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">METER - NET: Phase current ratio 			 98.52894681546738	 %, PF: 			 1	</t>
+          <t xml:space="preserve">METER - NET: Phase current ratio 			 98.63521400498946	 %, PF: 			 1	</t>
         </is>
       </c>
       <c r="G670" s="3" t="n">
-        <v>98.52894681546738</v>
+        <v>98.63521400498946</v>
       </c>
       <c r="H670" s="3" t="inlineStr"/>
     </row>
     <row r="671">
-      <c r="A671" s="3" t="inlineStr">
+      <c r="A671" s="2" t="inlineStr">
         <is>
           <t>S66001</t>
         </is>
       </c>
-      <c r="B671" s="3" t="inlineStr">
+      <c r="B671" s="2" t="inlineStr">
         <is>
           <t>Sheridan Solar</t>
         </is>
       </c>
-      <c r="C671" s="3" t="inlineStr">
+      <c r="C671" s="2" t="inlineStr">
         <is>
           <t>EnergyRatio</t>
         </is>
       </c>
-      <c r="D671" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E671" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F671" s="3" t="inlineStr"/>
-      <c r="G671" s="3" t="n">
-        <v>94.78846706234503</v>
-      </c>
-      <c r="H671" s="3" t="inlineStr"/>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail: 0.00 %
+INVERTER 1: High energy ratio: 			 1.1242728068014802	
+METER - NET: High energy ratio: 			 1.1016750065966565	</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>{'index': 0, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.1242728068014802\t', 'success': 0.0, 'hardwareKey': 'H460777', 'hardwareName': 'INVERTER 1', 'isAcknowledged': False}, {'index': 1, 'result': 3, 'detail': 'High energy ratio: \t\t\t 1.1016750065966565\t', 'success': 0.0, 'hardwareKey': 'H460775', 'hardwareName': 'METER - NET', 'isAcknowledged': False}</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="3" t="inlineStr">
@@ -26677,7 +26625,7 @@
       </c>
       <c r="F674" s="3" t="inlineStr"/>
       <c r="G674" s="3" t="n">
-        <v>96.26462997815753</v>
+        <v>100.2066605300221</v>
       </c>
       <c r="H674" s="3" t="inlineStr"/>
     </row>
@@ -30900,7 +30848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30958,7 +30906,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T21:55:02Z</t>
+          <t>2026-06-09T20:29:42Z</t>
         </is>
       </c>
     </row>
@@ -31050,15 +30998,15 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CheckHW; EnergyRatio</t>
+          <t>CheckHW; EnergyRatio; PVlosses</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:57:17Z</t>
+          <t>2026-06-09T23:38:42Z</t>
         </is>
       </c>
     </row>
@@ -31075,7 +31023,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Availability; InverterUptime; DefaultAlerts; DataCuration; EnergyRatio (+2 more)</t>
+          <t>Availability; InverterUptime; DefaultAlerts; DataCuration; EnergyRatio (+1 more)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -31083,7 +31031,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:21:58Z</t>
+          <t>2026-06-09T22:48:04Z</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31056,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T20:45:58Z</t>
+          <t>2026-06-09T19:29:48Z</t>
         </is>
       </c>
     </row>
@@ -31133,7 +31081,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T21:43:06Z</t>
+          <t>2026-06-09T20:17:43Z</t>
         </is>
       </c>
     </row>
@@ -31183,7 +31131,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T22:21:45Z</t>
+          <t>2026-06-09T20:48:45Z</t>
         </is>
       </c>
     </row>
@@ -31215,17 +31163,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>S54613</t>
+          <t>S54681</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Warbler</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Availability; InverterUptime</t>
+          <t>Availability; CheckUpload; NetworkCom; CheckHW; InvalidAlerts (+6 more)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -31233,24 +31181,24 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T22:14:01Z</t>
+          <t>2026-06-09T12:52:07Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>S54681</t>
+          <t>S59656</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Whitetail</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; NetworkCom; CheckHW; InvalidAlerts (+6 more)</t>
+          <t>Availability; CheckUpload; CheckHW; InvalidAlerts; CheckWeather (+3 more)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -31258,49 +31206,49 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T12:52:07Z</t>
+          <t>2026-06-09T07:07:20Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>S59656</t>
+          <t>S63837</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Whitetail</t>
+          <t>Bulloch 1B</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; CheckHW; InvalidAlerts; CheckWeather (+3 more)</t>
+          <t>CheckUpload; DefaultAlerts; Tracker</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T07:07:20Z</t>
+          <t>2026-06-09T05:47:44Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>S63837</t>
+          <t>S63838</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bulloch 1B</t>
+          <t>Bulloch 1A</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CheckUpload; DefaultAlerts; Tracker</t>
+          <t>DefaultAlerts; Tracker</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -31308,49 +31256,49 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T05:47:44Z</t>
+          <t>2026-06-09T17:01:44Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>S63838</t>
+          <t>S63839</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Bulloch 1A</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DefaultAlerts; Tracker</t>
+          <t>Availability; CheckHW; DefaultAlerts; Tracker; CorrectiveAction</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:01:44Z</t>
+          <t>2026-06-09T23:40:15Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>S63839</t>
+          <t>S63840</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Upson</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckHW; DefaultAlerts; Tracker; EnergyRatio (+1 more)</t>
+          <t>DefaultAlerts; CheckWeather; CheckPMCTs</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -31358,24 +31306,24 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T00:58:51Z</t>
+          <t>2026-06-09T03:50:49Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>S63840</t>
+          <t>S64602</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Upson</t>
+          <t>McLean</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DefaultAlerts; CheckWeather; CheckPMCTs</t>
+          <t>Availability; CheckUpload; CheckHW; DefaultAlerts; InvalidAlerts (+3 more)</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -31383,24 +31331,24 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T03:50:49Z</t>
+          <t>2026-06-09T12:51:40Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>S64602</t>
+          <t>S64603</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>McLean</t>
+          <t>Shorthorn</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; CheckHW; DefaultAlerts; InvalidAlerts (+3 more)</t>
+          <t>Availability; CheckUpload; CheckHW; DefaultAlerts; CheckWeather (+2 more)</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -31408,49 +31356,49 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T12:51:40Z</t>
+          <t>2026-06-09T21:21:59Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>S64603</t>
+          <t>S65216</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Shorthorn</t>
+          <t>Green Solar</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; CheckHW; DefaultAlerts; Tracker (+1 more)</t>
+          <t>EnergyRatio</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T23:14:06Z</t>
+          <t>2026-06-09T14:18:07Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>S65216</t>
+          <t>S65784</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Green Solar</t>
+          <t>Washington Solar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EnergyRatio</t>
+          <t>Availability; CheckHW; DefaultAlerts; DataCuration; Tracker (+3 more)</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -31458,24 +31406,24 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T14:18:07Z</t>
+          <t>2026-06-09T11:03:49Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>S65784</t>
+          <t>S65785</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Washington Solar</t>
+          <t>Harding Solar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckHW; DefaultAlerts; DataCuration; Tracker (+3 more)</t>
+          <t>Availability; CheckHW; DefaultAlerts; Tracker; PVlosses (+1 more)</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -31483,24 +31431,24 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T11:03:49Z</t>
+          <t>2026-05-29T06:08:36Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>S65785</t>
+          <t>S65786</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Harding Solar</t>
+          <t>Whitehall Solar</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckHW; DefaultAlerts; Tracker; PVlosses (+1 more)</t>
+          <t>Availability; DefaultAlerts; CheckWeather; Tracker</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -31508,24 +31456,24 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29T06:08:36Z</t>
+          <t>2026-05-26T06:02:47Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>S65786</t>
+          <t>S65787</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Whitehall Solar</t>
+          <t>Sunflower Solar</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Availability; DefaultAlerts; CheckWeather; Tracker</t>
+          <t>DefaultAlerts; CheckWeather; Tracker; EnergyRatio; PVlosses (+1 more)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -31533,74 +31481,74 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26T06:02:47Z</t>
+          <t>2026-06-09T16:12:22Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>S65787</t>
+          <t>S65788</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sunflower Solar</t>
+          <t>Gray Fox Solar</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DefaultAlerts; CheckWeather; Tracker; EnergyRatio; PVlosses (+1 more)</t>
+          <t>Availability; CheckUpload; InverterUptime; DefaultAlerts; Tracker (+2 more)</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T16:12:22Z</t>
+          <t>2026-06-01T05:58:41Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>S65788</t>
+          <t>S65918</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Gray Fox Solar</t>
+          <t>C &amp; B Graham Energy</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; InverterUptime; DefaultAlerts; Tracker (+2 more)</t>
+          <t>Availability; CheckUpload; NetworkCom; CheckHW; DefaultAlerts (+8 more)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01T05:58:41Z</t>
+          <t>2026-06-09T16:24:00Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>S65918</t>
+          <t>S66001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C &amp; B Graham Energy</t>
+          <t>Sheridan Solar</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; NetworkCom; CheckHW; DefaultAlerts (+8 more)</t>
+          <t>CheckWeather; EnergyRatio</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -31608,24 +31556,24 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T16:24:00Z</t>
+          <t>2026-06-09T18:09:41Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>S66001</t>
+          <t>S66930</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Sheridan Solar</t>
+          <t>Elk Solar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CheckWeather</t>
+          <t>Availability; CheckUpload; InverterUptime; CheckHW; CheckMeterVoltage (+8 more)</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -31633,24 +31581,24 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T19:56:57Z</t>
+          <t>2026-06-09T05:49:51Z</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>S66930</t>
+          <t>S68112</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Elk Solar</t>
+          <t>Wallace Solar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; InverterUptime; CheckHW; CheckMeterVoltage (+8 more)</t>
+          <t>CheckWeather; EnergyRatio</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -31658,80 +31606,55 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T05:49:51Z</t>
+          <t>2026-05-26T05:56:41Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>S68112</t>
+          <t>S70532</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Wallace Solar</t>
+          <t>Longleaf Pine Solar, LLC</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CheckWeather; EnergyRatio</t>
+          <t>Availability; CheckUpload; InverterUptime; AlertRecipients; CheckHW (+3 more)</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26T05:56:41Z</t>
+          <t>2026-06-09T03:37:29Z</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>S70532</t>
+          <t>S70645</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Longleaf Pine Solar, LLC</t>
+          <t>Williams Solar, LLC</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Availability; CheckUpload; InverterUptime; AlertRecipients; CheckHW (+3 more)</t>
+          <t>Availability; CheckUpload; InverterUptime; InvalidAlerts; EnergyRatio (+1 more)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09T03:37:29Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>S70645</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Williams Solar, LLC</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Availability; CheckUpload; InverterUptime; InvalidAlerts; EnergyRatio (+1 more)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2026-06-09T05:41:36Z</t>
         </is>
@@ -31792,14 +31715,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "runAt": "2026-06-08T21:55:02Z",</t>
+          <t xml:space="preserve">  "runAt": "2026-06-09T20:29:42Z",</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "lastChanged": "2026-06-08T21:55:07Z",</t>
+          <t xml:space="preserve">  "lastChanged": "2026-06-09T20:29:47Z",</t>
         </is>
       </c>
     </row>
@@ -33024,7 +32947,7 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "success": 97.66374454804765,</t>
+          <t xml:space="preserve">      "success": 96.50233209789944,</t>
         </is>
       </c>
     </row>
@@ -33129,14 +33052,14 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "detail": "Elkor MKII Production Meter: Phase current ratio \t\t\t 98.16743905668737\t %, PF: \t\t\t 0.9967669907722094\t",</t>
+          <t xml:space="preserve">      "detail": "Elkor MKII Production Meter: Phase current ratio \t\t\t 98.7899415135375\t %, PF: \t\t\t 0.9970237311753682\t",</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "success": 98.16743905668737,</t>
+          <t xml:space="preserve">      "success": 98.7899415135375,</t>
         </is>
       </c>
     </row>
@@ -33192,7 +33115,7 @@
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "success": 76.11583372395667,</t>
+          <t xml:space="preserve">      "success": 72.1128636475715,</t>
         </is>
       </c>
     </row>
@@ -33360,7 +33283,7 @@
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "success": 87.08311660951708,</t>
+          <t xml:space="preserve">      "success": 81.3287701293063,</t>
         </is>
       </c>
     </row>
